--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3726" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -338,338 +338,335 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Observation.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Observation.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Observation.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Observation.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:supportingInfo</t>
+  </si>
+  <si>
+    <t>supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
+</t>
+  </si>
+  <si>
+    <t>Other information that may be relevant to this event.</t>
+  </si>
+  <si>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Observation.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Observation.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Observation.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Observation.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Observation.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Observation.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Observation.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Observation.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Observation.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:supportingInfo</t>
-  </si>
-  <si>
-    <t>supportingInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
-</t>
-  </si>
-  <si>
-    <t>Other information that may be relevant to this event.</t>
-  </si>
-  <si>
-    <t>Autres ressources pertinentes *du dossier patient*</t>
-  </si>
-  <si>
-    <t>Observation.extension:MesReasonForMeasurement</t>
-  </si>
-  <si>
-    <t>MesReasonForMeasurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
-</t>
-  </si>
-  <si>
-    <t>Motif de la mesure</t>
-  </si>
-  <si>
-    <t>Motif de la mesure
-Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -680,7 +677,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -731,14 +728,7 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -767,7 +757,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -795,9 +785,6 @@
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>Codes providing the status of an observation.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
@@ -847,9 +834,6 @@
 value:coding.system}</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
@@ -977,9 +961,6 @@
   </si>
   <si>
     <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
@@ -1194,7 +1175,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1252,14 +1233,14 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
-    <t>ele-1
-vs-1</t>
+    <t xml:space="preserve">vs-1
+</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1287,7 +1268,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1337,7 +1318,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1349,8 +1330,8 @@
 &lt;/valueQuantity&gt;</t>
   </si>
   <si>
-    <t>ele-1
-obs-7vs-2</t>
+    <t>obs-7
+vs-2</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1462,17 +1443,14 @@
     <t>The identification of the system that provides the coded form of the unit.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
     <t>Quantity.system</t>
   </si>
   <si>
-    <t>ele-1
-qty-3</t>
+    <t xml:space="preserve">qty-3
+</t>
   </si>
   <si>
     <t>CO.codeSystem, PQ.translation.codeSystem</t>
@@ -1521,8 +1499,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>ele-1
-obs-6vs-2</t>
+    <t>obs-6
+vs-2</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1633,7 +1611,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1800,15 +1778,8 @@
     <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-3</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+    <t xml:space="preserve">obs-3
+</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1896,17 +1867,7 @@
     <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
   </si>
   <si>
-    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
-  </si>
-  <si>
     <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
@@ -1937,7 +1898,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1959,7 +1920,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1971,7 +1932,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -2028,7 +1989,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2037,8 +1998,8 @@
     <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common|4.0.1</t>
   </si>
   <si>
-    <t>ele-1
-vs-3</t>
+    <t xml:space="preserve">vs-3
+</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2057,8 +2018,8 @@
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
-    <t>ele-1
-obs-6vs-3</t>
+    <t>obs-6
+vs-3</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2895,11 +2856,11 @@
         <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
       </c>
@@ -2910,7 +2871,7 @@
         <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>82</v>
@@ -2921,10 +2882,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2947,13 +2908,13 @@
         <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3004,7 +2965,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -3028,7 +2989,7 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>82</v>
@@ -3039,14 +3000,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3065,16 +3026,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3112,19 +3073,19 @@
         <v>82</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -3133,10 +3094,10 @@
         <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -3148,7 +3109,7 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>82</v>
@@ -3159,10 +3120,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3188,13 +3149,13 @@
         <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3244,7 +3205,7 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -3253,11 +3214,11 @@
         <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
       </c>
@@ -3268,7 +3229,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3279,10 +3240,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3305,16 +3266,16 @@
         <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3364,7 +3325,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3373,11 +3334,11 @@
         <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
       </c>
@@ -3388,7 +3349,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3399,10 +3360,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3425,16 +3386,16 @@
         <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3484,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3493,11 +3454,11 @@
         <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
       </c>
@@ -3508,7 +3469,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3519,10 +3480,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3545,16 +3506,16 @@
         <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3604,7 +3565,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3613,11 +3574,11 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3628,7 +3589,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3639,10 +3600,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3665,16 +3626,16 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3700,31 +3661,31 @@
         <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3733,11 +3694,11 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3745,10 +3706,10 @@
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>82</v>
@@ -3759,10 +3720,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3785,16 +3746,16 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3820,13 +3781,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3844,7 +3805,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3853,11 +3814,11 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3865,10 +3826,10 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3879,10 +3840,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3905,16 +3866,16 @@
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3964,7 +3925,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3973,11 +3934,11 @@
         <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3988,7 +3949,7 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3999,10 +3960,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4025,16 +3986,16 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4060,13 +4021,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -4084,7 +4045,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4093,11 +4054,11 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
       </c>
@@ -4108,7 +4069,7 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -4119,14 +4080,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4145,16 +4106,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4204,7 +4165,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4213,11 +4174,11 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4228,7 +4189,7 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -4239,14 +4200,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4265,16 +4226,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4324,7 +4285,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4348,7 +4309,7 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -4359,14 +4320,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4385,17 +4346,15 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4432,19 +4391,17 @@
         <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC17" s="2"/>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4453,10 +4410,10 @@
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4468,7 +4425,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4479,13 +4436,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>82</v>
@@ -4507,13 +4464,13 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4564,7 +4521,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4573,10 +4530,10 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4599,13 +4556,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4627,13 +4584,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4684,7 +4641,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4693,10 +4650,10 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4719,14 +4676,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4745,19 +4702,19 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4794,19 +4751,19 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4815,10 +4772,10 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4830,7 +4787,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4841,10 +4798,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4867,17 +4824,17 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4926,7 +4883,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4935,25 +4892,25 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4961,14 +4918,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4987,19 +4944,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5048,7 +5003,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5057,22 +5012,22 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ22" t="s" s="2">
+      <c r="AK22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5083,14 +5038,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5109,16 +5064,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5168,7 +5123,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5177,22 +5132,22 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5203,10 +5158,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5229,19 +5184,19 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5266,13 +5221,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5290,7 +5243,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>93</v>
@@ -5299,25 +5252,25 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5325,10 +5278,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5351,19 +5304,19 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5388,29 +5341,29 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5419,11 +5372,11 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5431,13 +5384,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5445,13 +5398,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
@@ -5473,19 +5426,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5510,13 +5463,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5534,7 +5487,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5543,11 +5496,11 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5555,13 +5508,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5569,10 +5522,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5595,13 +5548,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5652,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5676,7 +5629,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5687,14 +5640,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5713,16 +5666,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5760,19 +5713,19 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC28" t="s" s="2">
+      <c r="AF28" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5781,10 +5734,10 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5796,7 +5749,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5807,10 +5760,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5833,19 +5786,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5894,7 +5847,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5903,11 +5856,11 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5915,10 +5868,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5929,10 +5882,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5955,13 +5908,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6012,7 +5965,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6036,7 +5989,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6047,14 +6000,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6073,16 +6026,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6120,19 +6073,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6141,10 +6094,10 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6156,7 +6109,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6167,10 +6120,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6193,26 +6146,26 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6254,7 +6207,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6263,11 +6216,11 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6275,10 +6228,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6289,10 +6242,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6315,16 +6268,16 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6374,7 +6327,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6383,11 +6336,11 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6395,10 +6348,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6409,10 +6362,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6435,26 +6388,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6496,7 +6447,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6505,11 +6456,11 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6517,10 +6468,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6531,10 +6482,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6557,19 +6508,17 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6618,7 +6567,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6627,11 +6576,11 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6639,10 +6588,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6653,10 +6602,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6679,19 +6628,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6740,7 +6689,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6749,11 +6698,11 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6761,10 +6710,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6775,10 +6724,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6801,19 +6750,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6862,7 +6811,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6871,11 +6820,11 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6883,10 +6832,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6897,14 +6846,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6923,19 +6872,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6960,13 +6909,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6984,7 +6933,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6993,36 +6942,36 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7045,13 +6994,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7102,7 +7051,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7126,7 +7075,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7137,14 +7086,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7163,16 +7112,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7210,19 +7159,19 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC40" t="s" s="2">
+      <c r="AF40" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7231,10 +7180,10 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7246,7 +7195,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7257,10 +7206,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7283,19 +7232,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7332,17 +7281,17 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7351,11 +7300,11 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7363,10 +7312,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7377,13 +7326,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7405,19 +7354,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7427,7 +7376,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7466,7 +7415,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7475,11 +7424,11 @@
         <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7487,10 +7436,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7501,10 +7450,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7527,19 +7476,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7588,7 +7537,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7597,11 +7546,11 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7609,10 +7558,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7623,10 +7572,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7649,19 +7598,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7710,7 +7659,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7719,25 +7668,25 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7745,10 +7694,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7771,16 +7720,16 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7830,7 +7779,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7839,11 +7788,11 @@
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7851,13 +7800,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7865,14 +7814,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7891,19 +7840,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7952,7 +7901,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7961,25 +7910,25 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK46" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7987,14 +7936,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8013,19 +7962,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8074,7 +8023,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8083,25 +8032,25 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8109,10 +8058,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8135,16 +8084,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8194,7 +8143,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8203,11 +8152,11 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8215,13 +8164,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8229,10 +8178,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8255,19 +8204,17 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8316,7 +8263,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8325,25 +8272,25 @@
         <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8351,10 +8298,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8377,19 +8324,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8399,7 +8346,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8438,7 +8385,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8447,36 +8394,36 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8499,13 +8446,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8556,7 +8503,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8580,7 +8527,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8591,14 +8538,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8617,16 +8564,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8664,19 +8611,19 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC52" t="s" s="2">
+      <c r="AF52" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8685,10 +8632,10 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8700,7 +8647,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8711,10 +8658,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8737,19 +8684,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8798,7 +8745,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8807,11 +8754,11 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8819,10 +8766,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8833,10 +8780,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8859,70 +8806,68 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8931,11 +8876,11 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8943,10 +8888,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8957,10 +8902,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8983,19 +8928,17 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9005,7 +8948,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -9044,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9053,11 +8996,11 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9065,10 +9008,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9079,10 +9022,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9105,19 +9048,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9166,7 +9107,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9175,10 +9116,10 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9187,10 +9128,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9201,10 +9142,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9227,19 +9168,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9288,7 +9229,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9297,11 +9238,11 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9309,10 +9250,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9323,10 +9264,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9349,19 +9290,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9386,13 +9327,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9410,7 +9351,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9419,10 +9360,10 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9431,10 +9372,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9445,10 +9386,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9471,13 +9412,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9528,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9552,7 +9493,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9563,14 +9504,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9589,16 +9530,16 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9636,19 +9577,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC60" t="s" s="2">
+      <c r="AF60" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9657,10 +9598,10 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9672,7 +9613,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9683,10 +9624,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9709,19 +9650,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9770,7 +9711,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9779,11 +9720,11 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9791,10 +9732,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9805,10 +9746,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9831,13 +9772,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9888,7 +9829,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9912,7 +9853,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9923,14 +9864,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9949,16 +9890,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9996,19 +9937,19 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AC63" t="s" s="2">
+      <c r="AF63" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10017,10 +9958,10 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10032,7 +9973,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10043,10 +9984,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10069,19 +10010,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10130,7 +10071,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10139,11 +10080,11 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10151,10 +10092,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10165,10 +10106,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10191,16 +10132,16 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10250,7 +10191,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10259,11 +10200,11 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10271,10 +10212,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10285,10 +10226,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10311,19 +10252,17 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10372,7 +10311,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10381,11 +10320,11 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10393,10 +10332,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10407,10 +10346,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10433,19 +10372,17 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10494,7 +10431,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10503,11 +10440,11 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10515,10 +10452,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10529,10 +10466,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10555,19 +10492,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10616,7 +10553,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10625,11 +10562,11 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10637,10 +10574,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10651,10 +10588,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10677,19 +10614,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10738,7 +10675,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10747,11 +10684,11 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10759,10 +10696,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10773,14 +10710,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10799,19 +10736,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10836,13 +10773,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10860,7 +10797,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10869,36 +10806,36 @@
         <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10921,19 +10858,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10982,7 +10919,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10991,11 +10928,11 @@
         <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11003,10 +10940,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11017,10 +10954,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11043,16 +10980,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11078,13 +11015,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11102,7 +11039,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11111,36 +11048,36 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11163,19 +11100,19 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11200,11 +11137,11 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11222,7 +11159,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11231,11 +11168,11 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ73" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11243,10 +11180,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11257,10 +11194,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11283,16 +11220,16 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11342,7 +11279,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11351,36 +11288,36 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ74" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11403,16 +11340,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11462,7 +11399,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11471,36 +11408,36 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ75" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11523,19 +11460,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11584,7 +11521,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11593,10 +11530,10 @@
         <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11605,10 +11542,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11619,10 +11556,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11645,13 +11582,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11702,7 +11639,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11726,7 +11663,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11737,14 +11674,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11763,16 +11700,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11810,19 +11747,19 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11831,10 +11768,10 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11846,7 +11783,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11857,14 +11794,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11883,19 +11820,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11944,7 +11881,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11953,10 +11890,10 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11968,7 +11905,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11979,10 +11916,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12005,17 +11942,15 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12064,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12073,10 +12008,10 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>573</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12085,10 +12020,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12099,10 +12034,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12125,17 +12060,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L81" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="M81" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12184,7 +12117,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12193,10 +12126,10 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>573</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12205,10 +12138,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12219,10 +12152,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12245,19 +12178,19 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12282,13 +12215,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12306,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12315,22 +12248,22 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ82" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12341,10 +12274,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12367,19 +12300,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12404,13 +12337,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12428,7 +12361,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12437,22 +12370,22 @@
         <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ83" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12463,10 +12396,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12489,19 +12422,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12550,7 +12481,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12559,11 +12490,11 @@
         <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ84" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12571,10 +12502,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12585,10 +12516,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12611,17 +12542,15 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12670,7 +12599,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12679,11 +12608,11 @@
         <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ85" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12691,10 +12620,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12705,10 +12634,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12731,16 +12660,16 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12790,7 +12719,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12799,11 +12728,11 @@
         <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ86" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12811,10 +12740,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12825,10 +12754,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12851,16 +12780,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12910,7 +12839,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12919,11 +12848,11 @@
         <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ87" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12931,10 +12860,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12945,10 +12874,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12971,19 +12900,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13032,7 +12961,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13041,10 +12970,10 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13053,10 +12982,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13067,10 +12996,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13093,13 +13022,13 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13150,7 +13079,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13174,7 +13103,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13185,14 +13114,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13211,16 +13140,16 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13258,19 +13187,19 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13279,10 +13208,10 @@
         <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13294,7 +13223,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13305,14 +13234,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13331,19 +13260,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13392,7 +13321,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13401,10 +13330,10 @@
         <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13416,7 +13345,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13427,10 +13356,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13453,19 +13382,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13490,13 +13419,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13514,7 +13443,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>93</v>
@@ -13523,25 +13452,25 @@
         <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ92" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -13549,10 +13478,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13575,19 +13504,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13612,13 +13541,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13636,7 +13565,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13645,36 +13574,36 @@
         <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13697,19 +13626,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13734,13 +13663,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13758,7 +13687,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13767,10 +13696,10 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13779,10 +13708,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13793,14 +13722,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13819,19 +13748,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13856,13 +13785,13 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13880,7 +13809,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13889,36 +13818,36 @@
         <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ95" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13944,16 +13873,16 @@
         <v>83</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14002,7 +13931,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14014,7 +13943,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14023,10 +13952,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -493,7 +493,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -517,7 +517,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -560,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -747,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -827,7 +827,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1082,7 +1082,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1165,7 +1165,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1496,7 +1496,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1561,7 +1561,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1617,7 +1617,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1659,7 +1659,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1768,7 +1768,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1818,7 +1818,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1851,7 +1851,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1888,7 +1888,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -5156,7 +5156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>263</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>269</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>282</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>300</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>336</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>358</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>385</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>414</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>468</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>518</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>535</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>610</v>
       </c>
@@ -13354,7 +13354,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>620</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>626</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>635</v>
       </c>
@@ -13966,12 +13966,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP96">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,11 +660,27 @@
   </si>
   <si>
     <t>Motif de la mesure
-Texte libre (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…)</t>
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1283,7 +1299,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2348,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP96"/>
+  <dimension ref="A1:AP97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
@@ -2361,7 +2377,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4679,43 +4695,41 @@
         <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4763,7 +4777,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4772,7 +4786,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -4787,7 +4801,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4805,7 +4819,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4818,23 +4832,25 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4883,7 +4899,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4895,22 +4911,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4918,14 +4934,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4944,17 +4960,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5003,7 +5019,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5018,19 +5034,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5038,14 +5054,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5064,18 +5080,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5123,7 +5139,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5138,16 +5154,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5156,48 +5172,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5221,11 +5235,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5243,13 +5259,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5258,30 +5274,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5292,31 +5308,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5341,35 +5357,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5378,34 +5394,32 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5414,7 +5428,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5426,19 +5440,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5466,28 +5480,26 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5511,35 +5523,37 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5548,16 +5562,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5581,13 +5599,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5605,19 +5623,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5629,10 +5647,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5640,21 +5658,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5666,17 +5684,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5713,31 +5729,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5758,48 +5774,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5835,19 +5849,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5859,7 +5873,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5868,10 +5882,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5880,12 +5894,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5893,31 +5907,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5965,19 +5983,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5986,10 +6004,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6000,21 +6018,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6026,17 +6044,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6073,31 +6089,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6118,134 +6134,132 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6253,13 +6267,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6268,24 +6282,26 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6327,7 +6343,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6348,24 +6364,24 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6373,13 +6389,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6388,24 +6404,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6447,7 +6463,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6468,10 +6484,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6480,12 +6496,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6493,13 +6509,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6508,24 +6524,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6567,7 +6583,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6588,10 +6604,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6602,10 +6618,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6628,19 +6644,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6689,7 +6703,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6710,10 +6724,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6724,10 +6738,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6750,19 +6764,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6811,7 +6825,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6832,10 +6846,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6844,26 +6858,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6872,19 +6886,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6909,13 +6923,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6933,10 +6947,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -6948,62 +6962,66 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7027,13 +7045,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7051,10 +7069,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7063,44 +7081,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>352</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7112,17 +7130,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7159,31 +7175,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7206,18 +7222,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7229,23 +7245,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7281,9 +7295,11 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7291,7 +7307,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7303,7 +7319,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7312,10 +7328,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7326,14 +7342,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7342,7 +7356,7 @@
         <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7357,16 +7371,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7376,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7403,19 +7417,17 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7436,10 +7448,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7450,18 +7462,20 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7476,19 +7490,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7498,7 +7512,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7537,13 +7551,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7558,10 +7572,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7570,12 +7584,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7583,13 +7597,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7598,19 +7612,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7659,7 +7673,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7674,30 +7688,30 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7705,13 +7719,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7720,18 +7734,20 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7779,13 +7795,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7794,19 +7810,19 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7814,21 +7830,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7840,20 +7856,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7901,13 +7915,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7916,44 +7930,44 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7962,19 +7976,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8023,7 +8037,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8032,50 +8046,50 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8084,18 +8098,20 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>392</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8143,7 +8159,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8152,25 +8168,25 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8178,10 +8194,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8192,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8204,18 +8220,18 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>409</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8263,13 +8279,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8278,30 +8294,30 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8312,10 +8328,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8324,19 +8340,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8346,7 +8360,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8385,45 +8399,45 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8437,25 +8451,29 @@
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>420</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8464,7 +8482,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8503,7 +8521,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>110</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8512,47 +8530,47 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>111</v>
+        <v>428</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8564,17 +8582,15 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8611,31 +8627,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8658,21 +8674,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8681,23 +8697,21 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>115</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>116</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8733,31 +8747,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8766,10 +8780,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>435</v>
+        <v>111</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8780,10 +8794,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8800,74 +8814,74 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8888,10 +8902,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8902,10 +8916,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8913,7 +8927,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -8922,33 +8936,35 @@
         <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8963,13 +8979,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8987,7 +9003,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9008,10 +9024,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9022,10 +9038,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9048,17 +9064,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9068,7 +9084,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9107,7 +9123,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9116,7 +9132,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9128,10 +9144,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9142,10 +9158,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9168,19 +9184,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9229,7 +9243,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9238,7 +9252,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9250,10 +9264,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9262,12 +9276,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9275,34 +9289,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9327,13 +9341,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9351,7 +9365,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9360,7 +9374,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9372,10 +9386,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>192</v>
+        <v>457</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9384,12 +9398,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9403,7 +9417,7 @@
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9412,16 +9426,20 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>108</v>
+        <v>474</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9445,13 +9463,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9469,7 +9487,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>110</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9478,10 +9496,10 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9490,10 +9508,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>111</v>
+        <v>481</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9504,21 +9522,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9530,17 +9548,15 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9577,31 +9593,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9624,14 +9640,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9647,23 +9663,21 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9699,19 +9713,19 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9723,7 +9737,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9732,10 +9746,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9746,10 +9760,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9760,7 +9774,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9769,19 +9783,23 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9829,19 +9847,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9850,10 +9868,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9864,21 +9882,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9890,17 +9908,15 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9937,31 +9953,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9984,21 +10000,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10007,23 +10023,21 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10059,31 +10073,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10092,10 +10106,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10106,10 +10120,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10117,7 +10131,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
@@ -10132,18 +10146,20 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10191,7 +10207,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10212,10 +10228,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10226,10 +10242,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10237,7 +10253,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
@@ -10252,18 +10268,18 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10311,7 +10327,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10332,10 +10348,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10346,10 +10362,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10357,7 +10373,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10372,17 +10388,17 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10431,7 +10447,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10452,10 +10468,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10466,10 +10482,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10492,19 +10508,17 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>319</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10553,7 +10567,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10574,10 +10588,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10588,10 +10602,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10614,19 +10628,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>324</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10675,7 +10689,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10696,10 +10710,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10710,21 +10724,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10733,22 +10747,22 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>490</v>
+        <v>334</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>491</v>
+        <v>335</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>492</v>
+        <v>336</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>493</v>
+        <v>337</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10773,13 +10787,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10797,13 +10811,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>488</v>
+        <v>338</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
@@ -10815,31 +10829,31 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>497</v>
+        <v>339</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>498</v>
+        <v>340</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10858,19 +10872,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>501</v>
+        <v>258</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10895,13 +10909,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10919,7 +10933,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10937,27 +10951,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10968,7 +10982,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10980,18 +10994,20 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>253</v>
+        <v>506</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11015,13 +11031,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11039,13 +11055,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11057,27 +11073,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11091,7 +11107,7 @@
         <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11100,20 +11116,18 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11137,11 +11151,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11159,7 +11175,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11177,27 +11193,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11211,7 +11227,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -11220,18 +11236,20 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11255,13 +11273,11 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11279,7 +11295,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11297,27 +11313,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AM74" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11331,7 +11347,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11340,16 +11356,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11399,7 +11415,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11417,27 +11433,27 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11448,10 +11464,10 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11460,20 +11476,18 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11521,45 +11535,45 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>550</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11570,7 +11584,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11582,16 +11596,20 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>550</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>108</v>
+        <v>551</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11639,19 +11657,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>110</v>
+        <v>549</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11660,10 +11678,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>111</v>
+        <v>557</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11674,21 +11692,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11700,17 +11718,15 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11759,19 +11775,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11794,14 +11810,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>556</v>
+        <v>113</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11814,26 +11830,24 @@
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>557</v>
+        <v>115</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>558</v>
+        <v>116</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11881,7 +11895,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>559</v>
+        <v>121</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11905,7 +11919,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11923,26 +11937,26 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>561</v>
+        <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>562</v>
@@ -11950,8 +11964,12 @@
       <c r="M80" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11999,19 +12017,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12020,10 +12038,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>566</v>
+        <v>192</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12034,10 +12052,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12060,13 +12078,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12117,7 +12135,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12126,7 +12144,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12138,10 +12156,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12152,10 +12170,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12178,20 +12196,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>253</v>
+        <v>566</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N82" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12215,13 +12229,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12239,7 +12253,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12248,7 +12262,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12257,13 +12271,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>498</v>
+        <v>575</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12274,10 +12288,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12288,7 +12302,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12300,19 +12314,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12337,13 +12351,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12361,13 +12375,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12379,13 +12393,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12396,10 +12410,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12410,7 +12424,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12422,17 +12436,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12457,13 +12473,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12481,13 +12497,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12499,13 +12515,13 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>592</v>
+        <v>503</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12516,10 +12532,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12542,7 +12558,7 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>593</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>594</v>
@@ -12551,7 +12567,9 @@
         <v>595</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12599,7 +12617,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12620,10 +12638,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12634,10 +12652,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12648,7 +12666,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12657,10 +12675,10 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>598</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>599</v>
@@ -12668,9 +12686,7 @@
       <c r="M86" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>601</v>
-      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12719,13 +12735,13 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
@@ -12740,10 +12756,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>602</v>
+        <v>570</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12754,10 +12770,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12780,16 +12796,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12839,7 +12855,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12860,24 +12876,24 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="B88" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12891,7 +12907,7 @@
         <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12900,20 +12916,18 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>545</v>
+        <v>610</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>611</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O88" t="s" s="2">
         <v>613</v>
       </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12961,7 +12975,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12973,33 +12987,33 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="AN88" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="B89" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13010,28 +13024,32 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>550</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>108</v>
+        <v>616</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13079,19 +13097,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>110</v>
+        <v>615</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13100,10 +13118,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>111</v>
+        <v>621</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13114,21 +13132,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13140,17 +13158,15 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13199,19 +13215,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13234,14 +13250,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>556</v>
+        <v>113</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13254,26 +13270,24 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>557</v>
+        <v>115</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>558</v>
+        <v>116</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O91" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13321,7 +13335,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>559</v>
+        <v>121</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13345,7 +13359,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13354,47 +13368,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>621</v>
+        <v>562</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>622</v>
+        <v>563</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>623</v>
+        <v>117</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>624</v>
+        <v>216</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13419,13 +13433,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13443,34 +13457,34 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>620</v>
+        <v>564</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>347</v>
+        <v>192</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -13478,10 +13492,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13489,7 +13503,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>93</v>
@@ -13504,19 +13518,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13544,10 +13558,10 @@
         <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>631</v>
+        <v>347</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>632</v>
+        <v>348</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13565,16 +13579,16 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13583,27 +13597,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>422</v>
+        <v>351</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>423</v>
+        <v>352</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13623,22 +13637,22 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>253</v>
+        <v>632</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13666,10 +13680,10 @@
         <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>473</v>
+        <v>636</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>474</v>
+        <v>637</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13687,7 +13701,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13696,7 +13710,7 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13705,22 +13719,22 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>192</v>
+        <v>427</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>640</v>
       </c>
@@ -13729,17 +13743,17 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13748,19 +13762,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>490</v>
+        <v>641</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>491</v>
+        <v>642</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>492</v>
+        <v>643</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13788,10 +13802,10 @@
         <v>151</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13815,10 +13829,10 @@
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13827,31 +13841,31 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>497</v>
+        <v>192</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13870,19 +13884,19 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>642</v>
+        <v>495</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>643</v>
+        <v>496</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13907,13 +13921,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13931,7 +13945,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13949,23 +13963,145 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>552</v>
+        <v>503</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP96">
+  <autoFilter ref="A1:AP97">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13975,7 +14111,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI96">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="644">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,22 +665,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2364,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP97"/>
+  <dimension ref="A1:AP96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
@@ -4695,41 +4679,43 @@
         <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4777,7 +4763,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4786,7 +4772,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -4801,7 +4787,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4819,7 +4805,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4832,25 +4818,23 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>114</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4899,7 +4883,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4911,22 +4895,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4934,14 +4918,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4960,17 +4944,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5019,7 +5003,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5034,19 +5018,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5054,14 +5038,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5080,18 +5064,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5139,7 +5123,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5154,16 +5138,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5172,46 +5156,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5235,13 +5221,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5259,13 +5243,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5274,30 +5258,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5308,31 +5292,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5357,35 +5341,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5394,32 +5378,34 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5428,7 +5414,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5440,19 +5426,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5480,26 +5466,28 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5523,37 +5511,35 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5562,20 +5548,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5599,13 +5581,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5623,19 +5605,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5647,10 +5629,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5658,21 +5640,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5684,15 +5666,17 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5729,31 +5713,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5774,46 +5758,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5849,19 +5835,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5873,7 +5859,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5882,10 +5868,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5894,12 +5880,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5907,35 +5893,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5983,19 +5965,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6004,10 +5986,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6018,21 +6000,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6044,15 +6026,17 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6089,31 +6073,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6134,52 +6118,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6209,31 +6195,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6242,10 +6228,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6254,12 +6240,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6267,13 +6253,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6282,26 +6268,24 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6343,7 +6327,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6364,10 +6348,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6376,12 +6360,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6389,13 +6373,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6404,24 +6388,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6463,7 +6447,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6484,10 +6468,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6496,12 +6480,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6509,13 +6493,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6524,24 +6508,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6583,7 +6567,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6604,10 +6588,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6618,10 +6602,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6644,17 +6628,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6703,7 +6689,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6724,10 +6710,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6738,10 +6724,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6764,19 +6750,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6825,7 +6811,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6846,10 +6832,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6858,26 +6844,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6886,19 +6872,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6923,13 +6909,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6947,10 +6933,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -6962,66 +6948,62 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7045,13 +7027,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7069,10 +7051,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7081,44 +7063,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>352</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7130,15 +7112,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7175,31 +7159,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7222,18 +7206,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7245,21 +7229,23 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7295,11 +7281,9 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7307,7 +7291,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7319,7 +7303,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7328,10 +7312,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7342,12 +7326,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7356,7 +7342,7 @@
         <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7371,16 +7357,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7390,7 +7376,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7417,17 +7403,19 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7448,10 +7436,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7462,20 +7450,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C43" t="s" s="2">
-        <v>360</v>
-      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7490,19 +7476,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7512,7 +7498,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7551,13 +7537,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7572,10 +7558,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7584,12 +7570,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7597,13 +7583,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7612,19 +7598,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7673,7 +7659,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7688,30 +7674,30 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7719,13 +7705,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7734,20 +7720,18 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7795,13 +7779,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7810,19 +7794,19 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7830,21 +7814,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7856,18 +7840,20 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7915,13 +7901,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7930,44 +7916,44 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7976,19 +7962,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8037,7 +8023,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8046,50 +8032,50 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8098,20 +8084,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8159,7 +8143,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8168,25 +8152,25 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>398</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8194,10 +8178,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8208,7 +8192,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8220,18 +8204,18 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>129</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8279,13 +8263,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8294,30 +8278,30 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8328,10 +8312,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8340,17 +8324,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8360,7 +8346,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8399,45 +8385,45 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8451,29 +8437,25 @@
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>108</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8482,7 +8464,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8521,7 +8503,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>110</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8530,47 +8512,47 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>111</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8582,15 +8564,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8627,31 +8611,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8674,21 +8658,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8697,21 +8681,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>114</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>115</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>116</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8747,31 +8733,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>121</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8780,10 +8766,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>111</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8794,10 +8780,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8814,30 +8800,30 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>433</v>
+        <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8857,13 +8843,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8881,7 +8867,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8902,10 +8888,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8916,10 +8902,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8927,7 +8913,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -8936,35 +8922,33 @@
         <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q55" t="s" s="2">
-        <v>445</v>
-      </c>
+      <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8979,13 +8963,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -9003,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9024,10 +9008,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9038,10 +9022,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9064,17 +9048,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9084,7 +9068,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9123,7 +9107,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9132,7 +9116,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9144,10 +9128,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9158,10 +9142,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9184,17 +9168,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9243,7 +9229,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9252,7 +9238,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9264,10 +9250,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9276,12 +9262,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9289,34 +9275,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9341,13 +9327,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9365,7 +9351,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9374,7 +9360,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9386,10 +9372,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>457</v>
+        <v>192</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9398,12 +9384,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9417,7 +9403,7 @@
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9426,20 +9412,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>108</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9463,13 +9445,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9487,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>110</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9496,10 +9478,10 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9508,10 +9490,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>481</v>
+        <v>111</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9522,21 +9504,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9548,15 +9530,17 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9593,31 +9577,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9640,14 +9624,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9663,21 +9647,23 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>115</v>
+        <v>271</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9713,19 +9699,19 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9737,7 +9723,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9746,10 +9732,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9760,10 +9746,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9774,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9783,23 +9769,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9847,19 +9829,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9868,10 +9850,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9882,21 +9864,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9908,15 +9890,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9953,31 +9937,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10000,21 +9984,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10023,21 +10007,23 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10073,31 +10059,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10106,10 +10092,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10120,10 +10106,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10131,7 +10117,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
@@ -10146,20 +10132,18 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10207,7 +10191,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10228,10 +10212,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10242,10 +10226,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10253,7 +10237,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
@@ -10268,18 +10252,18 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10327,7 +10311,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10348,10 +10332,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10362,10 +10346,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10373,7 +10357,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10388,17 +10372,17 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10447,7 +10431,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10468,10 +10452,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10482,10 +10466,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10508,17 +10492,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10567,7 +10553,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10588,10 +10574,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10602,10 +10588,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10628,19 +10614,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10689,7 +10675,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10710,10 +10696,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10724,21 +10710,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10747,22 +10733,22 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>334</v>
+        <v>490</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>335</v>
+        <v>491</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>336</v>
+        <v>492</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>337</v>
+        <v>493</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10787,13 +10773,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10811,13 +10797,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>338</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
@@ -10829,31 +10815,31 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>339</v>
+        <v>497</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>340</v>
+        <v>498</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10872,19 +10858,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>258</v>
+        <v>501</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10909,31 +10895,31 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10951,27 +10937,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10982,7 +10968,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10994,20 +10980,18 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>506</v>
+        <v>253</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11031,13 +11015,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11055,13 +11039,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11073,27 +11057,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11107,7 +11091,7 @@
         <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11116,18 +11100,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11151,31 +11137,29 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11193,27 +11177,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11227,7 +11211,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -11236,20 +11220,18 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>258</v>
+        <v>527</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11273,11 +11255,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11295,7 +11279,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11313,27 +11297,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11347,7 +11331,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11356,16 +11340,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11415,7 +11399,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11433,27 +11417,27 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11464,10 +11448,10 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11476,18 +11460,20 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11535,45 +11521,45 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>550</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11584,7 +11570,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11596,20 +11582,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>550</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>551</v>
+        <v>108</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11657,19 +11639,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>549</v>
+        <v>110</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11678,10 +11660,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>557</v>
+        <v>111</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11692,21 +11674,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11718,15 +11700,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11775,19 +11759,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11810,14 +11794,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>556</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11830,24 +11814,26 @@
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>557</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
+        <v>558</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11895,7 +11881,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>559</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11919,7 +11905,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11937,26 +11923,26 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>114</v>
+        <v>561</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>562</v>
@@ -11964,12 +11950,8 @@
       <c r="M80" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N80" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>216</v>
-      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12017,19 +11999,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI80" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ80" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12038,10 +12020,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>192</v>
+        <v>566</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12052,10 +12034,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12078,13 +12060,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12135,7 +12117,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12144,7 +12126,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12156,10 +12138,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12170,10 +12152,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12196,16 +12178,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>566</v>
+        <v>253</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12229,13 +12215,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12253,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12262,7 +12248,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12271,13 +12257,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>575</v>
+        <v>498</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12288,10 +12274,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12302,7 +12288,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12314,19 +12300,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12351,13 +12337,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12375,13 +12361,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12393,13 +12379,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12410,10 +12396,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12424,7 +12410,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12436,19 +12422,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>258</v>
+        <v>588</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12473,13 +12457,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12497,13 +12481,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12515,13 +12499,13 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>503</v>
+        <v>592</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12532,10 +12516,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12558,7 +12542,7 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>593</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>594</v>
@@ -12567,9 +12551,7 @@
         <v>595</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>596</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12617,7 +12599,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12638,10 +12620,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12652,10 +12634,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12666,7 +12648,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12675,10 +12657,10 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>598</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>599</v>
@@ -12686,7 +12668,9 @@
       <c r="M86" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N86" s="2"/>
+      <c r="N86" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12735,13 +12719,13 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
@@ -12756,10 +12740,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12770,10 +12754,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12796,16 +12780,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12855,7 +12839,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12876,10 +12860,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12888,12 +12872,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12907,7 +12891,7 @@
         <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12916,18 +12900,20 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>610</v>
+        <v>545</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>611</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12975,7 +12961,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12987,7 +12973,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>614</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12996,10 +12982,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13008,12 +12994,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13024,32 +13010,28 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>550</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>616</v>
+        <v>108</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13097,19 +13079,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>615</v>
+        <v>110</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13118,10 +13100,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>621</v>
+        <v>111</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13132,21 +13114,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13158,15 +13140,17 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13215,19 +13199,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13250,14 +13234,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>113</v>
+        <v>556</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13270,24 +13254,26 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>115</v>
+        <v>557</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>116</v>
+        <v>558</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13335,7 +13321,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>121</v>
+        <v>559</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13359,7 +13345,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13368,47 +13354,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>562</v>
+        <v>621</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>563</v>
+        <v>622</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>117</v>
+        <v>623</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>216</v>
+        <v>624</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13433,13 +13419,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13457,34 +13443,34 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>564</v>
+        <v>620</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -13492,10 +13478,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13503,7 +13489,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>93</v>
@@ -13518,19 +13504,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>258</v>
+        <v>627</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>629</v>
+        <v>418</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13558,10 +13544,10 @@
         <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>347</v>
+        <v>631</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>348</v>
+        <v>632</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13579,16 +13565,16 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13597,27 +13583,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13637,22 +13623,22 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>632</v>
+        <v>253</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13680,10 +13666,10 @@
         <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>636</v>
+        <v>473</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>637</v>
+        <v>474</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13701,7 +13687,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13710,7 +13696,7 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13719,22 +13705,22 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>639</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>427</v>
+        <v>192</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>428</v>
+        <v>476</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>640</v>
       </c>
@@ -13743,17 +13729,17 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13762,19 +13748,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>641</v>
+        <v>490</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>642</v>
+        <v>491</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>643</v>
+        <v>492</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13802,10 +13788,10 @@
         <v>151</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13829,10 +13815,10 @@
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13841,31 +13827,31 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>192</v>
+        <v>497</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13884,19 +13870,19 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>495</v>
+        <v>642</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>496</v>
+        <v>643</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>497</v>
+        <v>548</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>498</v>
+        <v>549</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13921,13 +13907,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13945,7 +13931,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13963,145 +13949,23 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>502</v>
+        <v>551</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>503</v>
+        <v>552</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP97">
+  <autoFilter ref="A1:AP96">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14111,7 +13975,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI95">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
